--- a/bieu-mau/thu-thap-du-lieu-truong.xlsx
+++ b/bieu-mau/thu-thap-du-lieu-truong.xlsx
@@ -18,7 +18,7 @@
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'0. HƯỚNG DẪN'!$A$1:$E$29</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'1. Thông tin trường'!$4:$4</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'1. Thông tin trường'!$A$1:$D$49</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'1. Thông tin trường'!$A$1:$D$52</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'2. Điểm trường &amp; Lớp học'!$15:$15</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'2. Điểm trường &amp; Lớp học'!$A$1:$L$51</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'3. Email đăng nhập'!$4:$4</definedName>
@@ -1378,7 +1378,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D49"/>
+  <dimension ref="A1:D52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1706,26 +1706,30 @@
     <row r="23" ht="24" customHeight="1">
       <c r="A23" s="31" t="inlineStr">
         <is>
-          <t>BI_THU_CHI_BO</t>
+          <t>TO_CHUC_DANG</t>
         </is>
       </c>
       <c r="B23" s="10" t="inlineStr">
         <is>
-          <t>Bí thư Chi bộ</t>
+          <t>Tổ chức đảng của trường</t>
         </is>
       </c>
       <c r="C23" s="32" t="inlineStr"/>
-      <c r="D23" s="11" t="inlineStr"/>
+      <c r="D23" s="11" t="inlineStr">
+        <is>
+          <t>Chọn trong danh sách. Từ 30 đảng viên trở lên thì lập đảng bộ cơ sở; dưới 30 vẫn lập được nhưng phải có văn bản đồng ý của cấp ủy cấp trên</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="24" customHeight="1">
       <c r="A24" s="31" t="inlineStr">
         <is>
-          <t>CT_CONG_DOAN</t>
+          <t>SO_DANG_VIEN</t>
         </is>
       </c>
       <c r="B24" s="10" t="inlineStr">
         <is>
-          <t>Chủ tịch Công đoàn</t>
+          <t>Số đảng viên chính thức</t>
         </is>
       </c>
       <c r="C24" s="32" t="inlineStr"/>
@@ -1734,388 +1738,438 @@
     <row r="25" ht="24" customHeight="1">
       <c r="A25" s="31" t="inlineStr">
         <is>
-          <t>TPT_DOI</t>
+          <t>SO_CHI_BO</t>
         </is>
       </c>
       <c r="B25" s="10" t="inlineStr">
         <is>
-          <t>Tổng phụ trách Đội</t>
+          <t>Số chi bộ trực thuộc</t>
         </is>
       </c>
       <c r="C25" s="32" t="inlineStr"/>
-      <c r="D25" s="11" t="inlineStr"/>
+      <c r="D25" s="11" t="inlineStr">
+        <is>
+          <t>Chỉ điền khi chọn Đảng bộ. Thường mỗi điểm trường một chi bộ, nhưng điểm dưới 3 đảng viên chính thức thì phải ghép</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="24" customHeight="1">
       <c r="A26" s="31" t="inlineStr">
         <is>
-          <t>TRUONG_BAN_CMHS</t>
+          <t>BI_THU_DANG</t>
         </is>
       </c>
       <c r="B26" s="10" t="inlineStr">
         <is>
-          <t>Trưởng ban đại diện cha mẹ học sinh</t>
+          <t>Bí thư Chi bộ / Đảng ủy — họ và tên</t>
         </is>
       </c>
       <c r="C26" s="32" t="inlineStr"/>
-      <c r="D26" s="11" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="15" t="inlineStr">
-        <is>
-          <t>C. TÌNH TRẠNG TRƯỜNG CHUẨN QUỐC GIA</t>
-        </is>
-      </c>
-      <c r="B27" s="16" t="n"/>
-      <c r="C27" s="16" t="n"/>
-      <c r="D27" s="17" t="n"/>
+      <c r="D26" s="11" t="inlineStr">
+        <is>
+          <t>Ghi đúng chức danh theo mô hình đã chọn ở trên</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="24" customHeight="1">
+      <c r="A27" s="31" t="inlineStr">
+        <is>
+          <t>CT_CONG_DOAN</t>
+        </is>
+      </c>
+      <c r="B27" s="10" t="inlineStr">
+        <is>
+          <t>Chủ tịch Công đoàn</t>
+        </is>
+      </c>
+      <c r="C27" s="32" t="inlineStr"/>
+      <c r="D27" s="11" t="inlineStr"/>
     </row>
     <row r="28" ht="24" customHeight="1">
       <c r="A28" s="31" t="inlineStr">
         <is>
-          <t>CNQG_MUC_DO</t>
+          <t>TPT_DOI</t>
         </is>
       </c>
       <c r="B28" s="10" t="inlineStr">
         <is>
-          <t>Mức đạt chuẩn quốc gia hiện tại</t>
+          <t>Tổng phụ trách Đội</t>
         </is>
       </c>
       <c r="C28" s="32" t="inlineStr"/>
-      <c r="D28" s="11" t="inlineStr">
-        <is>
-          <t>Chọn trong danh sách</t>
-        </is>
-      </c>
+      <c r="D28" s="11" t="inlineStr"/>
     </row>
     <row r="29" ht="24" customHeight="1">
       <c r="A29" s="31" t="inlineStr">
         <is>
-          <t>CNQG_SO_QD</t>
+          <t>TRUONG_BAN_CMHS</t>
         </is>
       </c>
       <c r="B29" s="10" t="inlineStr">
         <is>
-          <t>Số quyết định công nhận</t>
+          <t>Trưởng ban đại diện cha mẹ học sinh</t>
         </is>
       </c>
       <c r="C29" s="32" t="inlineStr"/>
       <c r="D29" s="11" t="inlineStr"/>
     </row>
-    <row r="30" ht="24" customHeight="1">
-      <c r="A30" s="31" t="inlineStr">
-        <is>
-          <t>CNQG_NGAY_KY</t>
-        </is>
-      </c>
-      <c r="B30" s="10" t="inlineStr">
-        <is>
-          <t>Ngày ký quyết định công nhận</t>
-        </is>
-      </c>
-      <c r="C30" s="32" t="inlineStr"/>
-      <c r="D30" s="11" t="inlineStr">
-        <is>
-          <t>dd/mm/yyyy</t>
-        </is>
-      </c>
+    <row r="30">
+      <c r="A30" s="15" t="inlineStr">
+        <is>
+          <t>C. TÌNH TRẠNG TRƯỜNG CHUẨN QUỐC GIA</t>
+        </is>
+      </c>
+      <c r="B30" s="16" t="n"/>
+      <c r="C30" s="16" t="n"/>
+      <c r="D30" s="17" t="n"/>
     </row>
     <row r="31" ht="24" customHeight="1">
       <c r="A31" s="31" t="inlineStr">
         <is>
-          <t>CNQG_HET_HAN</t>
+          <t>CNQG_MUC_DO</t>
         </is>
       </c>
       <c r="B31" s="10" t="inlineStr">
         <is>
-          <t>Ngày hết hạn công nhận</t>
+          <t>Mức đạt chuẩn quốc gia hiện tại</t>
         </is>
       </c>
       <c r="C31" s="32" t="inlineStr"/>
       <c r="D31" s="11" t="inlineStr">
         <is>
-          <t>Thường 5 năm kể từ ngày ký</t>
+          <t>Chọn trong danh sách</t>
         </is>
       </c>
     </row>
     <row r="32" ht="24" customHeight="1">
       <c r="A32" s="31" t="inlineStr">
         <is>
-          <t>CO_HOI_DONG_TDG</t>
+          <t>CNQG_SO_QD</t>
         </is>
       </c>
       <c r="B32" s="10" t="inlineStr">
         <is>
-          <t>Đã lập Hội đồng tự đánh giá chưa</t>
+          <t>Số quyết định công nhận</t>
         </is>
       </c>
       <c r="C32" s="32" t="inlineStr"/>
-      <c r="D32" s="11" t="inlineStr">
-        <is>
-          <t>Chọn Có / Không</t>
-        </is>
-      </c>
+      <c r="D32" s="11" t="inlineStr"/>
     </row>
     <row r="33" ht="24" customHeight="1">
       <c r="A33" s="31" t="inlineStr">
         <is>
-          <t>QD_HOI_DONG_TDG</t>
+          <t>CNQG_NGAY_KY</t>
         </is>
       </c>
       <c r="B33" s="10" t="inlineStr">
         <is>
-          <t>Số, ngày QĐ thành lập Hội đồng TĐG</t>
+          <t>Ngày ký quyết định công nhận</t>
         </is>
       </c>
       <c r="C33" s="32" t="inlineStr"/>
-      <c r="D33" s="11" t="inlineStr"/>
+      <c r="D33" s="11" t="inlineStr">
+        <is>
+          <t>dd/mm/yyyy</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="24" customHeight="1">
       <c r="A34" s="31" t="inlineStr">
         <is>
-          <t>BC_TDG_GAN_NHAT</t>
+          <t>CNQG_HET_HAN</t>
         </is>
       </c>
       <c r="B34" s="10" t="inlineStr">
         <is>
-          <t>Năm học của báo cáo TĐG gần nhất</t>
+          <t>Ngày hết hạn công nhận</t>
         </is>
       </c>
       <c r="C34" s="32" t="inlineStr"/>
-      <c r="D34" s="11" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="15" t="inlineStr">
-        <is>
-          <t>D. QUY MÔ NĂM HỌC HIỆN TẠI</t>
-        </is>
-      </c>
-      <c r="B35" s="16" t="n"/>
-      <c r="C35" s="16" t="n"/>
-      <c r="D35" s="17" t="n"/>
+      <c r="D34" s="11" t="inlineStr">
+        <is>
+          <t>Thường 5 năm kể từ ngày ký</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="24" customHeight="1">
+      <c r="A35" s="31" t="inlineStr">
+        <is>
+          <t>CO_HOI_DONG_TDG</t>
+        </is>
+      </c>
+      <c r="B35" s="10" t="inlineStr">
+        <is>
+          <t>Đã lập Hội đồng tự đánh giá chưa</t>
+        </is>
+      </c>
+      <c r="C35" s="32" t="inlineStr"/>
+      <c r="D35" s="11" t="inlineStr">
+        <is>
+          <t>Chọn Có / Không</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="24" customHeight="1">
       <c r="A36" s="31" t="inlineStr">
         <is>
-          <t>NAM_HOC</t>
+          <t>QD_HOI_DONG_TDG</t>
         </is>
       </c>
       <c r="B36" s="10" t="inlineStr">
         <is>
-          <t>Năm học hiện tại</t>
+          <t>Số, ngày QĐ thành lập Hội đồng TĐG</t>
         </is>
       </c>
       <c r="C36" s="32" t="inlineStr"/>
-      <c r="D36" s="11" t="inlineStr">
-        <is>
-          <t>2026-2027</t>
-        </is>
-      </c>
+      <c r="D36" s="11" t="inlineStr"/>
     </row>
     <row r="37" ht="24" customHeight="1">
       <c r="A37" s="31" t="inlineStr">
         <is>
-          <t>SO_LOP</t>
+          <t>BC_TDG_GAN_NHAT</t>
         </is>
       </c>
       <c r="B37" s="10" t="inlineStr">
         <is>
-          <t>Tổng số lớp</t>
+          <t>Năm học của báo cáo TĐG gần nhất</t>
         </is>
       </c>
       <c r="C37" s="32" t="inlineStr"/>
-      <c r="D37" s="11" t="inlineStr">
-        <is>
-          <t>Để đối chiếu với tệp CSDL ngành</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="24" customHeight="1">
-      <c r="A38" s="31" t="inlineStr">
-        <is>
-          <t>SO_HOC_SINH</t>
-        </is>
-      </c>
-      <c r="B38" s="10" t="inlineStr">
-        <is>
-          <t>Tổng số học sinh</t>
-        </is>
-      </c>
-      <c r="C38" s="32" t="inlineStr"/>
-      <c r="D38" s="11" t="inlineStr"/>
+      <c r="D37" s="11" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="15" t="inlineStr">
+        <is>
+          <t>D. QUY MÔ NĂM HỌC HIỆN TẠI</t>
+        </is>
+      </c>
+      <c r="B38" s="16" t="n"/>
+      <c r="C38" s="16" t="n"/>
+      <c r="D38" s="17" t="n"/>
     </row>
     <row r="39" ht="24" customHeight="1">
       <c r="A39" s="31" t="inlineStr">
         <is>
-          <t>SO_CBGV</t>
+          <t>NAM_HOC</t>
         </is>
       </c>
       <c r="B39" s="10" t="inlineStr">
         <is>
-          <t>Tổng số cán bộ quản lý, giáo viên, nhân viên</t>
+          <t>Năm học hiện tại</t>
         </is>
       </c>
       <c r="C39" s="32" t="inlineStr"/>
-      <c r="D39" s="11" t="inlineStr"/>
+      <c r="D39" s="11" t="inlineStr">
+        <is>
+          <t>2026-2027</t>
+        </is>
+      </c>
     </row>
     <row r="40" ht="24" customHeight="1">
       <c r="A40" s="31" t="inlineStr">
         <is>
-          <t>SO_DIEM_TRUONG</t>
+          <t>SO_LOP</t>
         </is>
       </c>
       <c r="B40" s="10" t="inlineStr">
         <is>
-          <t>Số cơ sở, phân hiệu, điểm trường</t>
+          <t>Tổng số lớp</t>
         </is>
       </c>
       <c r="C40" s="32" t="inlineStr"/>
       <c r="D40" s="11" t="inlineStr">
         <is>
-          <t>Trường một địa điểm ghi 1</t>
+          <t>Để đối chiếu với tệp CSDL ngành</t>
         </is>
       </c>
     </row>
     <row r="41" ht="24" customHeight="1">
       <c r="A41" s="31" t="inlineStr">
         <is>
-          <t>CO_SAP_NHAP</t>
+          <t>SO_HOC_SINH</t>
         </is>
       </c>
       <c r="B41" s="10" t="inlineStr">
         <is>
-          <t>Trường có sáp nhập từ các trường khác không</t>
+          <t>Tổng số học sinh</t>
         </is>
       </c>
       <c r="C41" s="32" t="inlineStr"/>
-      <c r="D41" s="11" t="inlineStr">
-        <is>
-          <t>Chọn Có / Không — nếu Có, điền thêm phần C trang 5</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="15" t="inlineStr">
-        <is>
-          <t>Đ. NHẬN DIỆN VÀ QUẢN TRỊ</t>
-        </is>
-      </c>
-      <c r="B42" s="16" t="n"/>
-      <c r="C42" s="16" t="n"/>
-      <c r="D42" s="17" t="n"/>
+      <c r="D41" s="11" t="inlineStr"/>
+    </row>
+    <row r="42" ht="24" customHeight="1">
+      <c r="A42" s="31" t="inlineStr">
+        <is>
+          <t>SO_CBGV</t>
+        </is>
+      </c>
+      <c r="B42" s="10" t="inlineStr">
+        <is>
+          <t>Tổng số cán bộ quản lý, giáo viên, nhân viên</t>
+        </is>
+      </c>
+      <c r="C42" s="32" t="inlineStr"/>
+      <c r="D42" s="11" t="inlineStr"/>
     </row>
     <row r="43" ht="24" customHeight="1">
       <c r="A43" s="31" t="inlineStr">
         <is>
-          <t>SLOGAN</t>
+          <t>SO_DIEM_TRUONG</t>
         </is>
       </c>
       <c r="B43" s="10" t="inlineStr">
         <is>
-          <t>Khẩu hiệu, phương châm của trường</t>
+          <t>Số cơ sở, phân hiệu, điểm trường</t>
         </is>
       </c>
       <c r="C43" s="32" t="inlineStr"/>
       <c r="D43" s="11" t="inlineStr">
         <is>
-          <t>Ví dụ: Vững bước tương lai - Tự tin hội nhập</t>
+          <t>Trường một địa điểm ghi 1</t>
         </is>
       </c>
     </row>
     <row r="44" ht="24" customHeight="1">
       <c r="A44" s="31" t="inlineStr">
         <is>
-          <t>MAU_CHU_DAO</t>
+          <t>CO_SAP_NHAP</t>
         </is>
       </c>
       <c r="B44" s="10" t="inlineStr">
         <is>
-          <t>Màu chủ đạo mong muốn cho trang</t>
+          <t>Trường có sáp nhập từ các trường khác không</t>
         </is>
       </c>
       <c r="C44" s="32" t="inlineStr"/>
       <c r="D44" s="11" t="inlineStr">
         <is>
-          <t>Ghi tên màu: xanh dương, xanh lá, đỏ đô…</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="24" customHeight="1">
-      <c r="A45" s="31" t="inlineStr">
-        <is>
-          <t>QUAN_TRI_TEN</t>
-        </is>
-      </c>
-      <c r="B45" s="10" t="inlineStr">
-        <is>
-          <t>Người phụ trách hệ thống phía trường — họ tên</t>
-        </is>
-      </c>
-      <c r="C45" s="32" t="inlineStr"/>
-      <c r="D45" s="11" t="inlineStr">
-        <is>
-          <t>Người được cấp quyền quản trị, tập huấn kỹ nhất</t>
-        </is>
-      </c>
+          <t>Chọn Có / Không — nếu Có, điền thêm phần C trang 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="15" t="inlineStr">
+        <is>
+          <t>Đ. NHẬN DIỆN VÀ QUẢN TRỊ</t>
+        </is>
+      </c>
+      <c r="B45" s="16" t="n"/>
+      <c r="C45" s="16" t="n"/>
+      <c r="D45" s="17" t="n"/>
     </row>
     <row r="46" ht="24" customHeight="1">
       <c r="A46" s="31" t="inlineStr">
         <is>
-          <t>QUAN_TRI_EMAIL</t>
+          <t>SLOGAN</t>
         </is>
       </c>
       <c r="B46" s="10" t="inlineStr">
         <is>
-          <t>Người phụ trách hệ thống — thư điện tử</t>
+          <t>Khẩu hiệu, phương châm của trường</t>
         </is>
       </c>
       <c r="C46" s="32" t="inlineStr"/>
-      <c r="D46" s="11" t="inlineStr"/>
+      <c r="D46" s="11" t="inlineStr">
+        <is>
+          <t>Ví dụ: Vững bước tương lai - Tự tin hội nhập</t>
+        </is>
+      </c>
     </row>
     <row r="47" ht="24" customHeight="1">
       <c r="A47" s="31" t="inlineStr">
         <is>
-          <t>CO_DRIVE</t>
+          <t>MAU_CHU_DAO</t>
         </is>
       </c>
       <c r="B47" s="10" t="inlineStr">
         <is>
-          <t>Trường đã có Google Drive dùng chung chưa</t>
+          <t>Màu chủ đạo mong muốn cho trang</t>
         </is>
       </c>
       <c r="C47" s="32" t="inlineStr"/>
       <c r="D47" s="11" t="inlineStr">
         <is>
-          <t>Chọn Có / Không</t>
+          <t>Ghi tên màu: xanh dương, xanh lá, đỏ đô…</t>
         </is>
       </c>
     </row>
     <row r="48" ht="24" customHeight="1">
       <c r="A48" s="31" t="inlineStr">
         <is>
+          <t>QUAN_TRI_TEN</t>
+        </is>
+      </c>
+      <c r="B48" s="10" t="inlineStr">
+        <is>
+          <t>Người phụ trách hệ thống phía trường — họ tên</t>
+        </is>
+      </c>
+      <c r="C48" s="32" t="inlineStr"/>
+      <c r="D48" s="11" t="inlineStr">
+        <is>
+          <t>Người được cấp quyền quản trị, tập huấn kỹ nhất</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="24" customHeight="1">
+      <c r="A49" s="31" t="inlineStr">
+        <is>
+          <t>QUAN_TRI_EMAIL</t>
+        </is>
+      </c>
+      <c r="B49" s="10" t="inlineStr">
+        <is>
+          <t>Người phụ trách hệ thống — thư điện tử</t>
+        </is>
+      </c>
+      <c r="C49" s="32" t="inlineStr"/>
+      <c r="D49" s="11" t="inlineStr"/>
+    </row>
+    <row r="50" ht="24" customHeight="1">
+      <c r="A50" s="31" t="inlineStr">
+        <is>
+          <t>CO_DRIVE</t>
+        </is>
+      </c>
+      <c r="B50" s="10" t="inlineStr">
+        <is>
+          <t>Trường đã có Google Drive dùng chung chưa</t>
+        </is>
+      </c>
+      <c r="C50" s="32" t="inlineStr"/>
+      <c r="D50" s="11" t="inlineStr">
+        <is>
+          <t>Chọn Có / Không</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="24" customHeight="1">
+      <c r="A51" s="31" t="inlineStr">
+        <is>
           <t>LINK_DRIVE</t>
         </is>
       </c>
-      <c r="B48" s="10" t="inlineStr">
+      <c r="B51" s="10" t="inlineStr">
         <is>
           <t>Đường dẫn thư mục Drive hiện có (nếu có)</t>
         </is>
       </c>
-      <c r="C48" s="32" t="inlineStr"/>
-      <c r="D48" s="11" t="inlineStr"/>
-    </row>
-    <row r="49" ht="24" customHeight="1">
-      <c r="A49" s="33" t="inlineStr">
+      <c r="C51" s="32" t="inlineStr"/>
+      <c r="D51" s="11" t="inlineStr"/>
+    </row>
+    <row r="52" ht="24" customHeight="1">
+      <c r="A52" s="33" t="inlineStr">
         <is>
           <t>GHI_CHU_TRUONG</t>
         </is>
       </c>
-      <c r="B49" s="25" t="inlineStr">
+      <c r="B52" s="25" t="inlineStr">
         <is>
           <t>Nguyện vọng khác của nhà trường</t>
         </is>
       </c>
-      <c r="C49" s="34" t="inlineStr"/>
-      <c r="D49" s="35" t="inlineStr">
+      <c r="C52" s="34" t="inlineStr"/>
+      <c r="D52" s="35" t="inlineStr">
         <is>
           <t>Ghi tự do</t>
         </is>
@@ -2125,17 +2179,20 @@
   <mergeCells count="7">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A5:D5"/>
-    <mergeCell ref="A27:D27"/>
-    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A45:D45"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A38:D38"/>
     <mergeCell ref="A16:D16"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A42:D42"/>
   </mergeCells>
-  <dataValidations count="2">
-    <dataValidation sqref="C28" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+  <dataValidations count="3">
+    <dataValidation sqref="C31" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>DM!$D$1:$D$3</formula1>
     </dataValidation>
-    <dataValidation sqref="C32 C41 C47" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="C23" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>DM!$G$1:$G$3</formula1>
+    </dataValidation>
+    <dataValidation sqref="C35 C44 C50" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>DM!$C$1:$C$2</formula1>
     </dataValidation>
   </dataValidations>
@@ -5752,7 +5809,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5784,6 +5841,11 @@
       <c r="F1" t="n">
         <v>1</v>
       </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Chi bộ</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -5814,6 +5876,11 @@
       <c r="F2" t="n">
         <v>2</v>
       </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Đảng bộ (có chi bộ trực thuộc)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -5838,6 +5905,11 @@
       </c>
       <c r="F3" t="n">
         <v>3</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Không có tổ chức đảng riêng</t>
+        </is>
       </c>
     </row>
     <row r="4">
